--- a/Server/Received_data/Model/Output_2.xlsx
+++ b/Server/Received_data/Model/Output_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,23 +442,23 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.90625</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>('FIX', 'Component_3')</t>
+          <t>('E2E3', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B3" t="n">
-        <v>0.875</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -468,153 +468,153 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B4" t="n">
-        <v>0.875</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>('Asm_280', 'Component_4')</t>
+          <t>('HIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B5" t="n">
-        <v>0.875</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>('HIX', 'Component_3')</t>
+          <t>('HIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B6" t="n">
-        <v>0.84375</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>('E2E3', 'HIX')</t>
+          <t>('Asm_350', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B7" t="n">
-        <v>0.84375</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>('C_org', 'HIX')</t>
+          <t>('E2E3', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B8" t="n">
-        <v>0.84375</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>('HIX', 'Component_1')</t>
+          <t>('FIX', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>0.84375</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>('Asm_350', 'HIX')</t>
+          <t>('C_org', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="B10" t="n">
-        <v>0.84375</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>('HIX', 'Component_4')</t>
+          <t>('Asm_350', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n">
-        <v>0.8125</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>('Asm_280', 'FIX')</t>
+          <t>('C_org', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8125</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>('FIX', 'HIX')</t>
+          <t>('FIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8125</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>('HIX', 'Component_2')</t>
+          <t>('Asm_280', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B14" t="n">
-        <v>0.8125</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Asm_280')</t>
+          <t>('Asm_280', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B15" t="n">
-        <v>0.78125</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -624,532 +624,402 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B16" t="n">
-        <v>0.78125</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>('Asm_280', 'Component_2')</t>
+          <t>('Suva', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="B17" t="n">
-        <v>0.78125</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>('Asm_350', 'FIX')</t>
+          <t>('C_org', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B18" t="n">
-        <v>0.78125</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Component_1')</t>
+          <t>('Asm_350', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B19" t="n">
-        <v>0.78125</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>('Asm_280', 'Component_1')</t>
+          <t>('C_org', 'Suva')</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B20" t="n">
-        <v>0.78125</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_280')</t>
+          <t>('E2E3', 'C_org')</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B21" t="n">
-        <v>0.78125</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>('C_org', 'Component_4')</t>
+          <t>('E2E3', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="B22" t="n">
-        <v>0.78125</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>('Component_2', 'Component_3')</t>
+          <t>('C_org', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B23" t="n">
-        <v>0.78125</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>('FIX', 'Component_1')</t>
+          <t>('Asm_350', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="B24" t="n">
-        <v>0.75</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>('C_org', 'Component_3')</t>
+          <t>('Asm_280', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B25" t="n">
-        <v>0.75</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>('Suva', 'HIX')</t>
+          <t>('C_org', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n">
-        <v>0.75</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_280')</t>
+          <t>('Asm_350', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="B27" t="n">
-        <v>0.75</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>('Component_1', 'Component_3')</t>
+          <t>('Suva', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="B28" t="n">
-        <v>0.71875</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>('Component_3', 'Component_4')</t>
+          <t>('Suva', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B29" t="n">
-        <v>0.71875</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Component_3')</t>
+          <t>('HIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B30" t="n">
-        <v>0.71875</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>('E2E3', 'Component_3')</t>
+          <t>('C_org', 'Asm_350')</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="B31" t="n">
-        <v>0.71875</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_280')</t>
+          <t>('Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B32" t="n">
-        <v>0.71875</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>('E2E3', 'Component_1')</t>
+          <t>('C_org', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n">
-        <v>0.6875</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>('C_org', 'FIX')</t>
+          <t>('FIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="B34" t="n">
-        <v>0.6875</v>
+        <v>0.5588235294117647</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>('Component_2', 'Component_4')</t>
+          <t>('Suva', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="B35" t="n">
-        <v>0.65625</v>
+        <v>0.5588235294117647</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>('Component_1', 'Component_4')</t>
+          <t>('E2E3', 'Suva')</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B36" t="n">
-        <v>0.65625</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>('C_org', 'Component_1')</t>
+          <t>('Suva', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="B37" t="n">
-        <v>0.65625</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>('Suva', 'Component_3')</t>
+          <t>('E2E3', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B38" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>('E2E3', 'C_org')</t>
+          <t>('E2E3', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B39" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>('E2E3', 'Component_4')</t>
+          <t>('Suva', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>('E2E3', 'FIX')</t>
+          <t>('Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B41" t="n">
-        <v>0.625</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>('C_org', 'Suva')</t>
+          <t>('Suva', 'Asm_350')</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="B42" t="n">
-        <v>0.59375</v>
+        <v>0.4411764705882353</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>('Suva', 'Component_2')</t>
+          <t>('Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="B43" t="n">
-        <v>0.59375</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>('Suva', 'Component_4')</t>
+          <t>('E2E3', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="B44" t="n">
-        <v>0.59375</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>('FIX', 'Component_4')</t>
+          <t>('E2E3', 'Asm_350')</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="B45" t="n">
-        <v>0.59375</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_350')</t>
+          <t>('FIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B46" t="n">
-        <v>0.59375</v>
+        <v>0.3235294117647059</v>
       </c>
       <c r="C46" t="inlineStr">
-        <is>
-          <t>('C_org', 'Component_2')</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B47" t="n">
-        <v>0.5625</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Asm_350')</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B48" t="n">
-        <v>0.5625</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Component_2')</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B49" t="n">
-        <v>0.5625</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>('FIX', 'Component_2')</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B50" t="n">
-        <v>0.5625</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>('Asm_350', 'Component_4')</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="B51" t="n">
-        <v>0.5625</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>('Component_1', 'Component_2')</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B52" t="n">
-        <v>0.5625</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>('Suva', 'Component_1')</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B53" t="n">
-        <v>0.53125</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>('Suva', 'FIX')</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B54" t="n">
-        <v>0.53125</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>('Suva', 'Asm_350')</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B55" t="n">
-        <v>0.53125</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Suva')</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B56" t="n">
-        <v>0.46875</v>
-      </c>
-      <c r="C56" t="inlineStr">
         <is>
           <t>('Asm_350', 'Component_2')</t>
         </is>

--- a/Server/Received_data/Model/Output_2.xlsx
+++ b/Server/Received_data/Model/Output_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,592 +436,732 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Feature</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7941176470588235</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>('E2E3', 'HIX')</t>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>('E2E3', 'C_org')</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7941176470588235</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>('Asm_280', 'HIX')</t>
+        <v>0.6060606060606061</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Suva')</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7941176470588235</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>('HIX', 'Component_3')</t>
+        <v>0.6060606060606061</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Asm_350')</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>('HIX', 'Component_1')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>('Asm_350', 'HIX')</t>
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>('E2E3', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7352941176470589</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Asm_280')</t>
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>('E2E3', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7352941176470589</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>('FIX', 'HIX')</t>
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7352941176470589</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>('C_org', 'Component_2')</t>
+        <v>0.4242424242424243</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>('Asm_350', 'Asm_280')</t>
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>('E2E3', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>('C_org', 'HIX')</t>
+        <v>0.696969696969697</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>('C_org', 'Suva')</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>('FIX', 'Component_3')</t>
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>('C_org', 'Asm_350')</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>('Asm_280', 'Component_1')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>('C_org', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>('Asm_280', 'FIX')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>('C_org', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>('Asm_280', 'Component_3')</t>
+        <v>0.696969696969697</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>('C_org', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>('Suva', 'HIX')</t>
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>('C_org', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>('C_org', 'Asm_280')</t>
+        <v>0.696969696969697</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>('C_org', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>('Asm_350', 'FIX')</t>
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>('C_org', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>('C_org', 'Suva')</t>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>('Suva', 'Asm_350')</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>('E2E3', 'C_org')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>('Suva', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Component_3')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>('Suva', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>('C_org', 'FIX')</t>
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>('Suva', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>('Asm_350', 'Component_1')</t>
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>('Suva', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>('Asm_280', 'Component_2')</t>
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>('Suva', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.6176470588235294</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>('C_org', 'Component_3')</t>
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>('Suva', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0.6176470588235294</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>('Asm_350', 'Component_3')</t>
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>('Asm_350', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0.6176470588235294</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>('Suva', 'Asm_280')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>('Asm_350', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>0.6176470588235294</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>('Suva', 'Component_2')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>('Asm_350', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0.6176470588235294</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>('HIX', 'Component_2')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>('Asm_350', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>('C_org', 'Asm_350')</t>
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>('Asm_350', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>('Component_1', 'Component_3')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>('Asm_350', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>('C_org', 'Component_1')</t>
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>('Asm_280', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>0.5882352941176471</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>('FIX', 'Component_1')</t>
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>('Asm_280', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>0.5588235294117647</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>('Suva', 'Component_3')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>('Asm_280', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>0.5588235294117647</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Suva')</t>
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>('Asm_280', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>0.5294117647058824</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>('Suva', 'Component_1')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>('Asm_280', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>0.5294117647058824</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Component_1')</t>
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>('FIX', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>('E2E3', 'FIX')</t>
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>('FIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>('Suva', 'FIX')</t>
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>('FIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>('Component_2', 'Component_3')</t>
+        <v>0.8787878787878788</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>('FIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>0.4705882352941176</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>('Suva', 'Asm_350')</t>
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>('HIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>0.4411764705882353</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>('Component_1', 'Component_2')</t>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>('HIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>0.4117647058823529</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Component_2')</t>
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>('HIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>0.4117647058823529</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>('E2E3', 'Asm_350')</t>
+        <v>0.696969696969697</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>('Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>0.3529411764705883</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>('FIX', 'Component_2')</t>
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>('Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>0.3235294117647059</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>('Asm_350', 'Component_2')</t>
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>('Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>

--- a/Server/Received_data/Model/Output_2.xlsx
+++ b/Server/Received_data/Model/Output_2.xlsx
@@ -447,721 +447,721 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>('E2E3', 'C_org')</t>
+          <t>('E2E3', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6060606060606061</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>('E2E3', 'Suva')</t>
+          <t>('Asm_280', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6060606060606061</v>
+        <v>0.7941176470588235</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_350')</t>
+          <t>('HIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>('E2E3', 'Asm_280')</t>
+          <t>('HIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>('E2E3', 'FIX')</t>
+          <t>('Asm_350', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B7" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>('E2E3', 'HIX')</t>
+          <t>('E2E3', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>('E2E3', 'Component_1')</t>
+          <t>('FIX', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4242424242424243</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>('E2E3', 'Component_2')</t>
+          <t>('C_org', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>('E2E3', 'Component_3')</t>
+          <t>('Asm_350', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n">
-        <v>0.696969696969697</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>('C_org', 'Suva')</t>
+          <t>('C_org', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_350')</t>
+          <t>('FIX', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B13" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>('C_org', 'Asm_280')</t>
+          <t>('Asm_280', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B14" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>('C_org', 'FIX')</t>
+          <t>('Asm_280', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="B15" t="n">
-        <v>0.696969696969697</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>('C_org', 'HIX')</t>
+          <t>('Asm_280', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>('C_org', 'Component_1')</t>
+          <t>('Suva', 'HIX')</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B17" t="n">
-        <v>0.696969696969697</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>('C_org', 'Component_2')</t>
+          <t>('C_org', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B18" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>('C_org', 'Component_3')</t>
+          <t>('Asm_350', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_350')</t>
+          <t>('C_org', 'Suva')</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="B20" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>('Suva', 'Asm_280')</t>
+          <t>('E2E3', 'C_org')</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B21" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>('Suva', 'FIX')</t>
+          <t>('E2E3', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B22" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>('Suva', 'HIX')</t>
+          <t>('C_org', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B23" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>('Suva', 'Component_1')</t>
+          <t>('Asm_350', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B24" t="n">
-        <v>0.5757575757575758</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>('Suva', 'Component_2')</t>
+          <t>('Asm_280', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B25" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>('Suva', 'Component_3')</t>
+          <t>('C_org', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Asm_280')</t>
+          <t>('Asm_350', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B27" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>('Asm_350', 'FIX')</t>
+          <t>('Suva', 'Asm_280')</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B28" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>('Asm_350', 'HIX')</t>
+          <t>('Suva', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B29" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Component_1')</t>
+          <t>('HIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="B30" t="n">
-        <v>0.5757575757575758</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Component_2')</t>
+          <t>('C_org', 'Asm_350')</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B31" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>('Asm_350', 'Component_3')</t>
+          <t>('Component_1', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B32" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>('Asm_280', 'FIX')</t>
+          <t>('C_org', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>('Asm_280', 'HIX')</t>
+          <t>('FIX', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B34" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.5588235294117647</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>('Asm_280', 'Component_1')</t>
+          <t>('Suva', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="B35" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.5588235294117647</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>('Asm_280', 'Component_2')</t>
+          <t>('E2E3', 'Suva')</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B36" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>('Asm_280', 'Component_3')</t>
+          <t>('Suva', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="B37" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>('FIX', 'HIX')</t>
+          <t>('E2E3', 'Component_1')</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="B38" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.5</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>('FIX', 'Component_1')</t>
+          <t>('E2E3', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="B39" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.5</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>('FIX', 'Component_2')</t>
+          <t>('Suva', 'FIX')</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.5</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>('FIX', 'Component_3')</t>
+          <t>('Component_2', 'Component_3')</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="B41" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>('HIX', 'Component_1')</t>
+          <t>('Suva', 'Asm_350')</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B42" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4411764705882353</v>
       </c>
       <c r="C42" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>('HIX', 'Component_2')</t>
+          <t>('Component_1', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="B43" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>('HIX', 'Component_3')</t>
+          <t>('E2E3', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="B44" t="n">
-        <v>0.696969696969697</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>('Component_1', 'Component_2')</t>
+          <t>('E2E3', 'Asm_350')</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B45" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="C45" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>('Component_1', 'Component_3')</t>
+          <t>('FIX', 'Component_2')</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B46" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.3235294117647059</v>
       </c>
       <c r="C46" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>('Component_2', 'Component_3')</t>
+          <t>('Asm_350', 'Component_2')</t>
         </is>
       </c>
     </row>
